--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487492_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487492_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3043</v>
+        <v>9.307700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3991</v>
+        <v>6.3757</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9052</v>
+        <v>2.9319</v>
       </c>
       <c r="G2" t="n">
         <v>8.4885</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4241</v>
+        <v>0.4274</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8763</v>
+        <v>-0.147</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5477</v>
+        <v>0.5745</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4257</v>
+        <v>3.6955</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2416</v>
+        <v>2.8323</v>
       </c>
       <c r="F3" t="n">
-        <v>1.184</v>
+        <v>0.8633</v>
       </c>
       <c r="G3" t="n">
         <v>5.2179</v>
@@ -688,13 +688,13 @@
         <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9324</v>
+        <v>0.2023</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1494</v>
+        <v>-0.5587</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0818</v>
+        <v>0.7611</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9412</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8858</v>
+        <v>3.6765</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6569</v>
+        <v>1.5546</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2288</v>
+        <v>2.1219</v>
       </c>
       <c r="G4" t="n">
         <v>2.4441</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3622</v>
+        <v>0.1529</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4288</v>
+        <v>-0.5311</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7909</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.8837</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9221</v>
+        <v>2.0198</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4428</v>
+        <v>2.6475</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.6276</v>
       </c>
       <c r="G5" t="n">
         <v>3.338</v>
@@ -844,13 +844,13 @@
         <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0231</v>
+        <v>0.0747</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.297</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.274</v>
+        <v>0.167</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2178</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5183</v>
+        <v>0.2894</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0443</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5626</v>
+        <v>1.0359</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9341</v>
+        <v>3.4148</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0258</v>
+        <v>2.6925</v>
       </c>
       <c r="I6" t="n">
-        <v>0.96</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7279</v>
+        <v>2.9919</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0408</v>
+        <v>3.5029</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6871</v>
+        <v>-0.5109</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2062</v>
+        <v>0.4229</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0667</v>
+        <v>-0.8104</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2729</v>
+        <v>1.2332</v>
       </c>
       <c r="P6" t="n">
         <v>-1.7626</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3468</v>
+        <v>0.6349</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1863</v>
+        <v>-0.257</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1606</v>
+        <v>0.8919</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.9977</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.4355</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0864</v>
+        <v>0.1712</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6363</v>
+        <v>-2.7387</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7228</v>
+        <v>2.9099</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0584</v>
@@ -1000,13 +1000,13 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>0.457</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0723</v>
+        <v>-0.1747</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5294</v>
+        <v>0.7165</v>
       </c>
       <c r="V7" t="n">
         <v>0.2754</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0404</v>
+        <v>-0.198</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1559</v>
+        <v>-0.7607</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1963</v>
+        <v>0.5626</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4148</v>
+        <v>0.9341</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6925</v>
+        <v>-0.0258</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9919</v>
+        <v>0.7279</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5029</v>
+        <v>0.0408</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5109</v>
+        <v>0.6871</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4229</v>
+        <v>0.2062</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8104</v>
+        <v>-0.0667</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2332</v>
+        <v>0.2729</v>
       </c>
       <c r="P8" t="n">
         <v>-1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3859</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6664</v>
+        <v>0.4699</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0523</v>
+        <v>0.1606</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9977</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4355</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4339</v>
+        <v>-2.8689</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3383</v>
+        <v>-1.8707</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0956</v>
+        <v>-0.9981</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2919</v>
+        <v>-0.8126</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6805</v>
+        <v>-0.3729</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3886</v>
+        <v>-0.4397</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4487</v>
+        <v>-1.0897</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6618000000000001</v>
+        <v>0.0323</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1105</v>
+        <v>-1.122</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7406</v>
+        <v>0.2771</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0187</v>
+        <v>-0.4052</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2781</v>
+        <v>0.6822</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1543</v>
+        <v>0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7123</v>
+        <v>0.3977</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6534</v>
+        <v>0.1982</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0589</v>
+        <v>0.1995</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2754</v>
+        <v>-3.0415</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2754</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.67</v>
+        <v>-2.9444</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4847</v>
+        <v>-2.929</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1852</v>
+        <v>-0.0154</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8126</v>
+        <v>-0.2919</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3729</v>
+        <v>-1.6805</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4397</v>
+        <v>1.3886</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0897</v>
+        <v>0.4487</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0323</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.122</v>
+        <v>1.1105</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2771</v>
+        <v>-0.7406</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4052</v>
+        <v>-1.0187</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6822</v>
+        <v>0.2781</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5875</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-3.1336</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4034</v>
+        <v>-0.2228</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4158</v>
+        <v>-0.2441</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0124</v>
+        <v>0.0213</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.0415</v>
+        <v>-0.2754</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0415</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1203</v>
+        <v>-4.1901</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0098</v>
+        <v>-5.2934</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8895</v>
+        <v>1.1034</v>
       </c>
       <c r="G11" t="n">
         <v>-3.201</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6232</v>
+        <v>0.307</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8734</v>
+        <v>-0.157</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2502</v>
+        <v>0.464</v>
       </c>
       <c r="V11" t="n">
         <v>-1.492</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.958799999999998</v>
+        <v>8.9587</v>
       </c>
       <c r="E12" t="n">
         <v>-0.9289000000000005</v>
       </c>
       <c r="F12" t="n">
-        <v>9.887699999999999</v>
+        <v>9.887800000000002</v>
       </c>
       <c r="G12" t="n">
         <v>19.4735</v>
@@ -1381,7 +1381,7 @@
         <v>8.8949</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.854699999999999</v>
+        <v>-6.8547</v>
       </c>
       <c r="Q12" t="n">
         <v>-20.5641</v>
@@ -1393,13 +1393,13 @@
         <v>3.1464</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4939</v>
+        <v>-1.4938</v>
       </c>
       <c r="U12" t="n">
         <v>4.640400000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.806500000000001</v>
+        <v>-6.8065</v>
       </c>
       <c r="W12" t="n">
         <v>2.0877</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.8424</v>
+        <v>7.1705</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2549</v>
+        <v>5.1526</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5875</v>
+        <v>2.0179</v>
       </c>
       <c r="G13" t="n">
         <v>4.099</v>
@@ -1468,13 +1468,13 @@
         <v>2.546</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0032</v>
+        <v>-0.675</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5652</v>
+        <v>-0.6675</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.438</v>
+        <v>-0.0075</v>
       </c>
       <c r="V13" t="n">
         <v>2.3756</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1883</v>
+        <v>2.6272</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4705</v>
+        <v>0.8799</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7178</v>
+        <v>1.7473</v>
       </c>
       <c r="G14" t="n">
         <v>1.1173</v>
@@ -1546,13 +1546,13 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7712</v>
+        <v>-0.3323</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7722</v>
+        <v>-0.3629</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0011</v>
+        <v>0.0306</v>
       </c>
       <c r="V14" t="n">
         <v>0.2754</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2801</v>
+        <v>0.4848</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7333</v>
+        <v>0.9379</v>
       </c>
       <c r="F15" t="n">
         <v>-0.4532</v>
@@ -1624,10 +1624,10 @@
         <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6293</v>
+        <v>-0.4246</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.111</v>
+        <v>-0.9063</v>
       </c>
       <c r="U15" t="n">
         <v>0.4817</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8108</v>
+        <v>-0.7038</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.0577</v>
+        <v>-3.0796</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2469</v>
+        <v>2.3759</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.476</v>
+        <v>-1.0362</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5612</v>
+        <v>0.4243</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.9147</v>
+        <v>-1.4605</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.6176</v>
+        <v>-1.8725</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.2936</v>
+        <v>-0.3964</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3241</v>
+        <v>-1.4761</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8583</v>
+        <v>0.8363</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2677</v>
+        <v>0.8208</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5906</v>
+        <v>0.0156</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1336</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1336</v>
+        <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1156</v>
+        <v>0.4499</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9261</v>
+        <v>-0.4652</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1895</v>
+        <v>0.9151</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5495</v>
+        <v>0.6659</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7673</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2178</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1472</v>
+        <v>-0.9821</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3866</v>
+        <v>-0.3662</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2394</v>
+        <v>-0.616</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0362</v>
+        <v>-1.2341</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4243</v>
+        <v>-0.0269</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4605</v>
+        <v>-1.2073</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8725</v>
+        <v>0.0408</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3964</v>
+        <v>0.0408</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4761</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8363</v>
+        <v>-1.275</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8208</v>
+        <v>-0.0677</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0156</v>
+        <v>-1.2073</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7834</v>
+        <v>0.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0065</v>
+        <v>-0.5314</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7722</v>
+        <v>-0.2111</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7786999999999999</v>
+        <v>-0.3202</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2403</v>
+        <v>-0.9969</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5708</v>
+        <v>0.1211</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6694</v>
+        <v>-1.118</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2341</v>
+        <v>-0.2357</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0269</v>
+        <v>2.4821</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2073</v>
+        <v>-2.7178</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0408</v>
+        <v>2.4413</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0408</v>
+        <v>3.1591</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.7178</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.275</v>
+        <v>-2.677</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0677</v>
+        <v>-0.677</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2073</v>
+        <v>-2</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7895</v>
+        <v>-0.1529</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4158</v>
+        <v>-0.3617</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3737</v>
+        <v>0.2088</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6451</v>
+        <v>-2.5461</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3906</v>
+        <v>-1.9204</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2545</v>
+        <v>-0.6256</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2357</v>
+        <v>-1.7357</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4821</v>
+        <v>-0.5233</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7178</v>
+        <v>-1.2125</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4413</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1591</v>
+        <v>0.0204</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7178</v>
+        <v>-0.6822</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.677</v>
+        <v>-1.0739</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.677</v>
+        <v>-0.5437</v>
       </c>
       <c r="O19" t="n">
-        <v>-2</v>
+        <v>-0.5302</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9585</v>
+        <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.801</v>
+        <v>-0.4186</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8734</v>
+        <v>-0.2794</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0723</v>
+        <v>-0.1392</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6262</v>
+        <v>-2.5908</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9204</v>
+        <v>-0.249</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7058</v>
+        <v>-2.3418</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7357</v>
+        <v>-2.5681</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5233</v>
+        <v>1.0693</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2125</v>
+        <v>-3.6374</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6618000000000001</v>
+        <v>1.4068</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0204</v>
+        <v>2.089</v>
       </c>
       <c r="L20" t="n">
         <v>-0.6822</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0739</v>
+        <v>-3.9748</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5437</v>
+        <v>-1.0197</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5302</v>
+        <v>-2.9551</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5875</v>
+        <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4988</v>
+        <v>-0.2601</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2794</v>
+        <v>-0.21</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2194</v>
+        <v>-0.0501</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0315</v>
+        <v>-3.2068</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.556</v>
+        <v>-5.0021</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4755</v>
+        <v>1.7953</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5681</v>
+        <v>-5.476</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0693</v>
+        <v>-2.5612</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6374</v>
+        <v>-2.9147</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4068</v>
+        <v>-3.6176</v>
       </c>
       <c r="K21" t="n">
-        <v>2.089</v>
+        <v>-2.2936</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6822</v>
+        <v>-1.3241</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.9748</v>
+        <v>-1.8583</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0197</v>
+        <v>-0.2677</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9551</v>
+        <v>-1.5906</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9377</v>
+        <v>-3.1336</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9585</v>
+        <v>3.1336</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7008</v>
+        <v>0.7196</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.517</v>
+        <v>-0.0182</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1838</v>
+        <v>0.7378</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2166</v>
+        <v>1.5495</v>
       </c>
       <c r="W21" t="n">
-        <v>1.492</v>
+        <v>1.7673</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2754</v>
+        <v>-0.2178</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7567</v>
+        <v>-3.6765</v>
       </c>
       <c r="E22" t="n">
         <v>-4.0928</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3361</v>
+        <v>0.4163</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0567</v>
@@ -2170,13 +2170,13 @@
         <v>3.3294</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5582</v>
+        <v>-0.478</v>
       </c>
       <c r="T22" t="n">
         <v>-0.387</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1712</v>
+        <v>-0.091</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2754</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0118</v>
+        <v>-3.856</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3715</v>
+        <v>-2.2692</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6402</v>
+        <v>-1.5868</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6115</v>
@@ -2248,13 +2248,13 @@
         <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.3608</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8734</v>
+        <v>-0.7711</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3568</v>
+        <v>0.4102</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2754</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.9588</v>
+        <v>-8.2765</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.887699999999999</v>
+        <v>-9.8878</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9291000000000005</v>
+        <v>1.611300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-19.4734</v>
@@ -2299,7 +2299,7 @@
         <v>-23.5409</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4320000000000001</v>
+        <v>-0.4320000000000005</v>
       </c>
       <c r="K24" t="n">
         <v>8.4628</v>
@@ -2326,13 +2326,13 @@
         <v>20.5639</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.1465</v>
+        <v>-2.4642</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.6405</v>
+        <v>-4.6404</v>
       </c>
       <c r="U24" t="n">
-        <v>1.494</v>
+        <v>2.1762</v>
       </c>
       <c r="V24" t="n">
         <v>6.806399999999999</v>
@@ -2341,7 +2341,7 @@
         <v>8.8942</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.087799999999999</v>
+        <v>-2.0878</v>
       </c>
     </row>
   </sheetData>
